--- a/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina est dans sa chambre. Un petit écran est allumé. Des couleurs bougent. Papa entre. Il s'assoit près du lit. Papa dit : fini. L'adulte dit fini. Lina écoute. Parce que papa a dit fini, elle va éteindre. Lina éteint. L'écran devient noir. Elle pose la télécommande. Papa dit : on prend un autre jeu. Lina choisit son puzzle. Les pièces sentent le carton. Papa et Lina posent les pièces. Une tour apparaît. Lina dit : l'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.</t>
+          <t>Lina est dans sa chambre. Un petit écran est allumé. Des couleurs bougent. Papa entre. Il s'assoit près du lit. Fini. L'adulte dit fini. Lina écoute. Parce que papa a dit fini, elle va éteindre. Lina éteint. L'écran devient noir. Elle pose la télécommande. On prend un autre jeu. Lina choisit son puzzle. Les pièces sentent le carton. Papa et Lina posent les pièces. Une tour apparaît. L'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lina est dans sa chambre. Un petit écran est allumé. Des couleurs bougent. Papa entre. Il s'assoit près du lit.
+papa|Fini. L'adulte dit fini.
+narrateur|Lina écoute. Parce que papa a dit fini, elle va éteindre. Lina éteint. L'écran devient noir. Elle pose la télécommande.
+papa|On prend un autre jeu.
+narrateur|Lina choisit son puzzle. Les pièces sentent le carton. Papa et Lina posent les pièces. Une tour apparaît.
+enfant-f|L'écran est éteint.
+narrateur|Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Lina ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Le puzzle était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lina range une pièce. Papa range la boîte. Merci, dit Lina.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Papa dit fini. Que fait Lina ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Lina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Le puzzle était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Lina range une pièce. Papa range la boîte. Merci, dit Lina.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lina éteint et choisit un jeu</t>
+          <t>Le doudou et le puzzle</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le doudou attend sur l'oreiller. Papa dit fini. Victorina éteint. Ils posent les pièces du puzzle. Une maison apparaît.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina est dans sa chambre. Un petit écran est allumé. Des couleurs bougent. Papa entre. Il s'assoit près du lit. Fini. L'adulte dit fini. Lina écoute. Parce que papa a dit fini, elle va éteindre. Lina éteint. L'écran devient noir. Elle pose la télécommande. On prend un autre jeu. Lina choisit son puzzle. Les pièces sentent le carton. Papa et Lina posent les pièces. Une tour apparaît. L'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Le rideau respire avec le vent. Victorina vit ici, avec papa et maman. Maman est à la cuisine, tout près. La chambre sent le linge propre. En ce moment, un petit écran est allumé. Des couleurs bougent. Victorina est assise près du lit. Papa entre. Il s'assoit près du lit. Victorina. Fini. Victorina écoute. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Mon puzzle. Les pièces sentent le carton. Elles sont un peu rudes. Papa et Victorina posent les pièces. Une maison apparaît. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Tu as entendu le carton ? Oui. Ça fait chh. Ils ajoutent un toit. Le doudou regarde, sur l'oreiller. On range les pièces ? Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Tu as su éteindre. Tu as choisi un autre jeu. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1325,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lina est dans sa chambre. Un petit écran est allumé. Des couleurs bougent. Papa entre. Il s'assoit près du lit.
-papa|Fini. L'adulte dit fini.
-narrateur|Lina écoute. Parce que papa a dit fini, elle va éteindre. Lina éteint. L'écran devient noir. Elle pose la télécommande.
+          <t>narrateur|Le doudou attend sur l'oreiller.
+narrateur|Il a une oreille un peu pliée.
+narrateur|Le rideau respire avec le vent.
+narrateur|Victorina vit ici, avec papa et maman.
+narrateur|Maman est à la cuisine, tout près.
+narrateur|La chambre sent le linge propre.
+narrateur|En ce moment, un petit écran est allumé.
+narrateur|Des couleurs bougent.
+narrateur|Victorina est assise près du lit.
+narrateur|Papa entre.
+narrateur|Il s'assoit près du lit.
+papa|Victorina.
+papa|Fini.
+narrateur|Victorina écoute.
+narrateur|Elle éteint.
+narrateur|L'écran devient noir.
+narrateur|Elle pose la télécommande.
+papa|Bravo, Victorina.
+papa|Tu as éteint.
 papa|On prend un autre jeu.
-narrateur|Lina choisit son puzzle. Les pièces sentent le carton. Papa et Lina posent les pièces. Une tour apparaît.
+papa|Tu vas choisir ?
+enfant-f|Mon puzzle.
+narrateur|Les pièces sentent le carton.
+narrateur|Elles sont un peu rudes.
+narrateur|Papa et Victorina posent les pièces.
+narrateur|Une maison apparaît.
 enfant-f|L'écran est éteint.
-narrateur|Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.</t>
+papa|Oui.
+papa|Un autre jeu, c'est bien.
+papa|Bravo.
+papa|Tu as entendu le carton ?
+enfant-f|Oui.
+enfant-f|Ça fait chh.
+narrateur|Ils ajoutent un toit.
+narrateur|Le doudou regarde, sur l'oreiller.
+papa|On range les pièces ?
+narrateur|Victorina range une pièce.
+narrateur|Papa range la boîte.
+enfant-f|Merci, papa.
+papa|Merci, Victorina.
+papa|Tu as su éteindre.
+papa|Tu as choisi un autre jeu.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>puzzle,rideau</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa dit fini. Que fait Lina ?</t>
+          <t>Papa dit fini. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1555,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa dit fini. Que fait Lina ?</t>
+          <t>narrateur|Papa dit fini.
+narrateur|Que fait Victorina ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Le puzzle était là.</t>
+          <t>Victorina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Tu as éteint ? Oui, papa. J'ai pris le puzzle. Bravo, Victorina. Quand on dit fini, on éteint. Puis on prend un autre jeu. Le puzzle était là. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1728,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Le puzzle était là.</t>
+          <t>narrateur|Victorina a éteint.
+narrateur|Papa avait dit fini.
+narrateur|Elle a pris un autre jeu.
+papa|Tu as éteint ?
+enfant-f|Oui, papa.
+enfant-f|J'ai pris le puzzle.
+papa|Bravo, Victorina.
+papa|Quand on dit fini, on éteint.
+papa|Puis on prend un autre jeu.
+narrateur|Le puzzle était là.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lina range une pièce. Papa range la boîte. Merci, dit Lina.</t>
+          <t>Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Le doudou attend encore. Tu lui racontes le puzzle ? Oui. On a fait une maison. On reste encore un peu ? Oui. Le rideau respire encore. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1902,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lina range une pièce. Papa range la boîte. Merci, dit Lina.</t>
+          <t>narrateur|Victorina range une pièce.
+narrateur|Papa range la boîte.
+enfant-f|Merci, papa.
+papa|Merci, Victorina.
+narrateur|Le doudou attend encore.
+papa|Tu lui racontes le puzzle ?
+enfant-f|Oui.
+enfant-f|On a fait une maison.
+papa|On reste encore un peu ?
+enfant-f|Oui.
+narrateur|Le rideau respire encore.
+papa|Tu as éteint.
+papa|Tu as choisi un autre jeu.
+papa|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1943,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Papa a dit fini. J'ai éteint. On a fait le puzzle. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2083,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Papa a dit fini.
+enfant-f|J'ai éteint.
+enfant-f|On a fait le puzzle.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Le rideau respire avec le vent. Victorina vit ici, avec papa et maman. Maman est à la cuisine, tout près. La chambre sent le linge propre. En ce moment, un petit écran est allumé. Des couleurs bougent. Victorina est assise près du lit. Papa entre. Il s'assoit près du lit. Victorina. Fini. Victorina écoute. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Mon puzzle. Les pièces sentent le carton. Elles sont un peu rudes. Papa et Victorina posent les pièces. Une maison apparaît. L'écran est éteint. Oui. Un autre jeu, c'est bien. Bravo. Tu as entendu le carton ? Oui. Ça fait chh. Ils ajoutent un toit. Le doudou regarde, sur l'oreiller. On range les pièces ? Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Tu as su éteindre. Tu as choisi un autre jeu. C'est du bon travail.</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Le rideau respire avec le vent. Victorina vit ici, avec papa et maman. Maman est à la cuisine, tout près. La chambre sent le linge propre. Une petite veilleuse fait un rond. Des chaussettes attendent près du lit. Sur la petite table, des couleurs bougent. Un petit écran est allumé. Victorina est assise près du lit. Elle tient le doudou d'une main. Papa pousse la porte. La porte fait un petit bruit. Il s'assoit près du lit. Victorina. Fini. Victorina écoute. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Mon puzzle. Les pièces sentent le carton. Elles sont un peu rudes. Sur la boîte, une maison. Tu as vu le toit rouge ? Oui. Et la porte bleue. Papa et Victorina posent les pièces. Une maison apparaît. L'écran est éteint. Oui. Le puzzle, c'est un beau jeu. Bravo. Tu as entendu le carton ? Oui. Ça fait chh. Ils ajoutent un toit. Le toit est rouge. Le doudou regarde, sur l'oreiller. Il regarde, hein ? Oui. Il attend. On range les pièces ? Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Tu as su éteindre. Tu as choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina est dans sa chambre. Un petit écran est allumé. Des couleurs bougent. Papa entre. Il s'assoit près du lit. Papa dit : fini. L'adulte dit fini. Lina écoute. Parce que papa a dit fini, elle va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Lina éteint. L'écran devient noir. Elle pose la télécommande. Papa dit : on prend un autre jeu. Lina choisit son puzzle. Les pièces sentent le carton. Papa et Lina posent les pièces. Une tour apparaît. Lina dit : l'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Ils ajoutent un toit. Puis ils rangent. Lina a su éteindre. Elle a choisi un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le doudou attend sur l'oreiller. Il a une oreille un peu pliée. Le rideau respire avec le vent. Victorina vit ici, avec papa et maman. Maman est à la cuisine, tout près. La chambre sent le linge propre. Une petite veilleuse fait un rond. Des chaussettes attendent près du lit. Sur la petite table, des couleurs bougent. Un petit écran est allumé. Victorina est assise près du lit. Elle tient le doudou d'une main. Papa pousse la porte. La porte fait un petit bruit. Il s'assoit près du lit. Victorina. Fini. Victorina écoute. Elle éteint. L'écran devient noir. Elle pose la télécommande. Bravo, Victorina. Tu as éteint. On prend un autre jeu. Tu vas choisir ? Mon puzzle. Les pièces sentent le carton. Elles sont un peu rudes. Sur la boîte, une maison. Tu as vu le toit rouge ? Oui. Et la porte bleue. Papa et Victorina posent les pièces. Une maison apparaît. L'écran est éteint. Oui. Le puzzle, c'est un beau jeu. Bravo. Tu as entendu le carton ? Oui. Ça fait chh. Ils ajoutent un toit. Le toit est rouge. Le doudou regarde, sur l'oreiller. Il regarde, hein ? Oui. Il attend. On range les pièces ? Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Tu as su éteindre. Tu as choisi un autre jeu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1331,10 +1331,14 @@
 narrateur|Victorina vit ici, avec papa et maman.
 narrateur|Maman est à la cuisine, tout près.
 narrateur|La chambre sent le linge propre.
-narrateur|En ce moment, un petit écran est allumé.
-narrateur|Des couleurs bougent.
+narrateur|Une petite veilleuse fait un rond.
+narrateur|Des chaussettes attendent près du lit.
+narrateur|Sur la petite table, des couleurs bougent.
+narrateur|Un petit écran est allumé.
 narrateur|Victorina est assise près du lit.
-narrateur|Papa entre.
+narrateur|Elle tient le doudou d'une main.
+narrateur|Papa pousse la porte.
+narrateur|La porte fait un petit bruit.
 narrateur|Il s'assoit près du lit.
 papa|Victorina.
 papa|Fini.
@@ -1349,25 +1353,32 @@
 enfant-f|Mon puzzle.
 narrateur|Les pièces sentent le carton.
 narrateur|Elles sont un peu rudes.
+narrateur|Sur la boîte, une maison.
+papa|Tu as vu le toit rouge ?
+enfant-f|Oui.
+enfant-f|Et la porte bleue.
 narrateur|Papa et Victorina posent les pièces.
 narrateur|Une maison apparaît.
 enfant-f|L'écran est éteint.
 papa|Oui.
-papa|Un autre jeu, c'est bien.
+papa|Le puzzle, c'est un beau jeu.
 papa|Bravo.
 papa|Tu as entendu le carton ?
 enfant-f|Oui.
 enfant-f|Ça fait chh.
 narrateur|Ils ajoutent un toit.
+narrateur|Le toit est rouge.
 narrateur|Le doudou regarde, sur l'oreiller.
+papa|Il regarde, hein ?
+enfant-f|Oui.
+enfant-f|Il attend.
 papa|On range les pièces ?
 narrateur|Victorina range une pièce.
 narrateur|Papa range la boîte.
 enfant-f|Merci, papa.
 papa|Merci, Victorina.
 papa|Tu as su éteindre.
-papa|Tu as choisi un autre jeu.
-papa|C'est du bon travail.</t>
+papa|Tu as choisi un autre jeu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1404,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa dit fini. Que fait Lina ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa dit fini. Que fait Victorina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1559,7 +1570,6 @@
 narrateur|Que fait Victorina ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1584,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Tu as éteint ? Oui, papa. J'ai pris le puzzle. Bravo, Victorina. Quand on dit fini, on éteint. Puis on prend un autre jeu. Le puzzle était là. C'est du bon travail.</t>
+          <t>Victorina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Tu as éteint ? Oui, papa. J'ai pris le puzzle. Bravo, Victorina. Quand on dit fini, on éteint. Puis on prend un autre jeu. Le puzzle était là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina a éteint. Papa avait dit fini. Elle a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. Le puzzle était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a éteint. Papa avait dit fini. Elle a pris un autre jeu. Tu as éteint ? Oui, papa. J'ai pris le puzzle. Bravo, Victorina. Quand on dit fini, on éteint. Puis on prend un autre jeu. Le puzzle était là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,11 +1747,9 @@
 papa|Bravo, Victorina.
 papa|Quand on dit fini, on éteint.
 papa|Puis on prend un autre jeu.
-narrateur|Le puzzle était là.
-papa|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|Le puzzle était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1766,12 +1774,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Le doudou attend encore. Tu lui racontes le puzzle ? Oui. On a fait une maison. On reste encore un peu ? Oui. Le rideau respire encore. Tu as éteint. Tu as choisi un autre jeu. Bravo.</t>
+          <t>Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Le doudou attend encore. Tu lui racontes le puzzle ? Oui. On a fait une maison. On reste encore un peu ? Oui. Le rideau respire encore. Le doudou a vu la maison. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina range une pièce. Papa range la boîte. Merci, dit Lina.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina range une pièce. Papa range la boîte. Merci, papa. Merci, Victorina. Le doudou attend encore. Tu lui racontes le puzzle ? Oui. On a fait une maison. On reste encore un peu ? Oui. Le rideau respire encore. Le doudou a vu la maison. Bravo.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1913,12 +1921,10 @@
 papa|On reste encore un peu ?
 enfant-f|Oui.
 narrateur|Le rideau respire encore.
-papa|Tu as éteint.
-papa|Tu as choisi un autre jeu.
+papa|Le doudou a vu la maison.
 papa|Bravo.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1943,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit fini. J'ai éteint. On a fait le puzzle. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Papa a dit fini. J'ai éteint. On a fait le puzzle. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a dit fini. J'ai éteint. On a fait le puzzle. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2086,12 +2092,9 @@
           <t>enfant-f|Papa a dit fini.
 enfant-f|J'ai éteint.
 enfant-f|On a fait le puzzle.
-papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2110,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2155,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-03.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lina, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
